--- a/corpus/legacy/addin/ext-name-src.xlsx
+++ b/corpus/legacy/addin/ext-name-src.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boris\source\workbench\docxy-issue-888\corpus\legacy\addin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boris\source\workbench\docxy-issue-890\corpus\legacy\addin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55B8D36E-51FE-45B3-9184-4AB7393DEABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D1E8E8F-7620-4B02-922B-D141CB63BEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{B8124728-B8FF-4B0F-BEFB-872785B63008}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{E82DEDC0-34A2-43D6-9799-CFCDACEE9512}"/>
   </bookViews>
   <sheets>
     <sheet name="P" sheetId="1" r:id="rId1"/>
@@ -408,7 +408,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE5E614-B5E6-4ECD-A753-22FE126ABC65}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E055C130-FE8B-43C8-A378-F398C96570C9}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
